--- a/results/reliability_eval/Llama-3-8B_P1412_sample_15_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P1412_sample_15_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.4298925488814515</v>
+        <v>0.3941573071775846</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1700304453872862</v>
+        <v>0.05250540233979908</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4298925488814515</v>
+        <v>0.3941573071775846</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1700304453872862</v>
+        <v>0.05250540233979908</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5600408405587197</v>
+        <v>0.6105859633074147</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2869369487470185</v>
+        <v>0.2229518574779786</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9912936540556762</v>
+        <v>0.995417661906456</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9587207946926617</v>
+        <v>0.924973544973545</v>
       </c>
       <c r="I2" t="n">
-        <v>0.189</v>
+        <v>0.063</v>
       </c>
     </row>
   </sheetData>
